--- a/diseases/d127/2015-2019.xlsx
+++ b/diseases/d127/2015-2019.xlsx
@@ -5885,6 +5885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12580,6 +12585,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12728,6 +12738,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12876,6 +12891,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13024,6 +13044,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13172,6 +13197,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13320,6 +13350,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13468,6 +13503,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13616,6 +13656,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13764,6 +13809,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13912,6 +13962,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14060,6 +14115,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19317,6 +19377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26801,6 +26866,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27345,6 +27415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27889,6 +27964,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28433,6 +28513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28977,6 +29062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29521,6 +29611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30065,6 +30160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30609,6 +30709,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31153,6 +31258,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31697,6 +31807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32241,6 +32356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37894,6 +38014,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44985,6 +45110,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45133,6 +45263,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45281,6 +45416,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45429,6 +45569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45577,6 +45722,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45725,6 +45875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45873,6 +46028,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46021,6 +46181,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46169,6 +46334,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46317,6 +46487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46465,6 +46640,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51722,6 +51902,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58810,6 +58995,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58958,6 +59148,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59106,6 +59301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59254,6 +59454,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59402,6 +59607,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59550,6 +59760,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59698,6 +59913,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59846,6 +60066,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59994,6 +60219,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60142,6 +60372,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60290,6 +60525,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65547,6 +65787,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72635,6 +72880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72783,6 +73033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72931,6 +73186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73079,6 +73339,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73227,6 +73492,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73375,6 +73645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73523,6 +73798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73671,6 +73951,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73819,6 +74104,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73967,6 +74257,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74113,6 +74408,11 @@
       <c r="S388" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO388" t="inlineStr">

--- a/diseases/d127/2015-2019.xlsx
+++ b/diseases/d127/2015-2019.xlsx
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
@@ -27232,7 +27232,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
@@ -27781,7 +27781,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -28330,7 +28330,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
@@ -29977,7 +29977,7 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
@@ -30526,7 +30526,7 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
@@ -31075,7 +31075,7 @@
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH160" t="inlineStr">
@@ -31624,7 +31624,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH163" t="inlineStr">
@@ -32173,7 +32173,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH166" t="inlineStr">
@@ -32722,7 +32722,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH169" t="inlineStr">
@@ -34898,7 +34898,7 @@
         </is>
       </c>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         </is>
       </c>
       <c r="AT181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
@@ -42569,7 +42569,7 @@
       </c>
       <c r="AG219" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH219" t="inlineStr">
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="AT253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
@@ -62671,7 +62671,7 @@
         </is>
       </c>
       <c r="AT326" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU326" t="inlineStr">
         <is>
@@ -62905,7 +62905,7 @@
         </is>
       </c>
       <c r="AT327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
